--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -678,12 +678,142 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -698,122 +698,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -698,12 +698,82 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,56 +448,56 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,188 +507,212 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>4.75</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.70</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>15.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -698,7 +722,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -708,7 +732,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -718,7 +742,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -728,7 +752,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -738,7 +762,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -748,7 +772,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -758,7 +782,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -768,12 +792,132 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,188 +448,188 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>17.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,126 +639,234 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -768,12 +876,112 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -962,26 +962,6 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,520 +448,90 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4.60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0Y1WIvRG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>f92vnwe3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4.65</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>5.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>GOO6q4Wr</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>xhKUdf9L</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,90 +448,388 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>15.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.20</t>
-        </is>
-      </c>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,29 +448,29 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -480,261 +480,213 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
-      </c>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -744,7 +696,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -754,7 +706,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -764,7 +716,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -774,7 +726,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -784,52 +736,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,300 +448,354 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
           <t>YN50iYWr</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,352 +448,220 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>2.80</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>9.00</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,181 +485,71 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>9.50</t>
         </is>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,78 +448,78 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YeqTho8m</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>08zpk37C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>8EcB5Oig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,29 +529,139 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.80</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -590,12 +590,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,9 +661,205 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.80</t>
-        </is>
-      </c>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,418 +448,134 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YeqTho8m</t>
+          <t>SfxxiPx0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>08zpk37C</t>
+          <t>na927pNt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CjIFsr1e</t>
+          <t>dzUhmsxP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8EcB5Oig</t>
+          <t>SdHeBgOE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jckS1tiI</t>
+          <t>fVeJ32M5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>na927pNt</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8b5vHIeT</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xjut9IFr</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IRBb0lXA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYbQEmn4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4b2YCRGG</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>xWrPG9Hi</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ImLNuMV7</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>dCNk2A2b</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OAmz0KLU</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pxdwg6Pp</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>QiF6bS1N</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>2.80</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,134 +448,564 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>8b5vHIeT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>xjut9IFr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>IRBb0lXA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>dYbQEmn4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>4b2YCRGG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>2.75</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>2.80</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,564 +448,200 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>dYbQEmn4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8b5vHIeT</t>
+          <t>4b2YCRGG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>xjut9IFr</t>
+          <t>xWrPG9Hi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IRBb0lXA</t>
+          <t>ImLNuMV7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>19.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYbQEmn4</t>
+          <t>dCNk2A2b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4b2YCRGG</t>
+          <t>OAmz0KLU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xWrPG9Hi</t>
+          <t>pxdwg6Pp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ImLNuMV7</t>
+          <t>QiF6bS1N</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>dCNk2A2b</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OAmz0KLU</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pxdwg6Pp</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>QiF6bS1N</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
           <t>4.50</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ddsD5q9j</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>QDjsB5oT</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>bqbA3PNE</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6VWd5zF7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,134 +448,520 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>13.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>2.80</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,520 +448,178 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>445r4WXo</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rkN7RQV9</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bwZsTw7E</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>f5SjRHyR</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ddsD5q9j</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QDjsB5oT</t>
+          <t>bqbA3PNE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bqbA3PNE</t>
+          <t>6VWd5zF7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6VWd5zF7</t>
+          <t>pGrl7dpe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>0AJjqex0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>40FWnYcm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>KApUeTtI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>EB22wLQj</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CQIvoCSa</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>4Ef51XCt</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>hzRnqjcC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>YgnMckC5</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>CvbDaBsg</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,520 +448,200 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>445r4WXo</t>
+          <t>06X4YYrf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rkN7RQV9</t>
+          <t>hMoEUjrJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bwZsTw7E</t>
+          <t>KSw0hfzQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>f5SjRHyR</t>
+          <t>YemQuHjK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ddsD5q9j</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QDjsB5oT</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bqbA3PNE</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6VWd5zF7</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pGrl7dpe</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>0AJjqex0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>40FWnYcm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>KApUeTtI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>EB22wLQj</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CQIvoCSa</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>4Ef51XCt</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>hzRnqjcC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>YgnMckC5</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>CvbDaBsg</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>2.50</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,198 +448,110 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.50</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,110 +448,286 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.25</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -448,286 +448,286 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>4.10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,286 +448,440 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.50</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
@@ -568,12 +568,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -695,17 +695,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -761,17 +761,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -475,12 +475,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,440 +448,110 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>0SQqjbAd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QqTA4cPk</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vymauDyP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>x88gL4RQ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dhkQFrkl</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8Sp1FEw8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4zlpJdvq</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>02sgHz9e</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>naHJ2yf2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>842EOIGL</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>jiAoNQdE</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>E595Qvn9</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,110 +448,440 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>3.70</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>5.25</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4.33</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,227 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>4.33</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,188 +448,188 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>02cHDDPH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>4z48FZf5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>dA00HeQh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>YFePBifU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>zHmSVfun</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>17.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,29 +639,249 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jFGHcfig</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>2.90</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.55</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ia5ItCg4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -480,12 +480,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -497,391 +497,127 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>19.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
           <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bXuieB8c</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Ia5ItCg4</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.83</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,176 +448,220 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>15.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>4.33</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>13.00</t>
         </is>
       </c>
     </row>
@@ -507,161 +507,249 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>3.10</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.75</t>
         </is>
       </c>
     </row>
